--- a/HDF5_files.xlsx
+++ b/HDF5_files.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guido\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guido\Desktop\Nuova cartella\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB697C26-7276-4134-9C40-28269AB899F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0036A524-B848-4E67-9A8B-F21A37DE7502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="128">
   <si>
     <t>4h cryo quiet acquisition</t>
   </si>
@@ -42,9 +42,6 @@
     <t>2025_01_02_07-06-04.h5</t>
   </si>
   <si>
-    <t>Y factor test + offset_PS6/offsetVD0</t>
-  </si>
-  <si>
     <t>2025_03_06_17-30-33.h5</t>
   </si>
   <si>
@@ -114,9 +111,6 @@
     <t>2025_04_09_16-51-21.h5</t>
   </si>
   <si>
-    <t>4h cryo quiet acquisition (new bias)</t>
-  </si>
-  <si>
     <t>FILE NAME</t>
   </si>
   <si>
@@ -129,9 +123,6 @@
     <t>2025_04_15_09-52-41.h5</t>
   </si>
   <si>
-    <t>2025_04_15_13-52-41.h5</t>
-  </si>
-  <si>
     <t>2025_04_15_14-08-47.h5</t>
   </si>
   <si>
@@ -159,12 +150,6 @@
     <t>Turn on/off board I</t>
   </si>
   <si>
-    <t>X-talk test on board Y polarimeters</t>
-  </si>
-  <si>
-    <t>2025_06_12_12-29-08.h5</t>
-  </si>
-  <si>
     <t>2025_06_12_13-29-11.h5</t>
   </si>
   <si>
@@ -174,9 +159,6 @@
     <t>4h warm quiet acquisition with POL_PWR=0-&gt;1 (all bias off) for pol R6</t>
   </si>
   <si>
-    <t>Turn on all boards (except B board)</t>
-  </si>
-  <si>
     <t>2025_06_13_06-49-09.h5</t>
   </si>
   <si>
@@ -193,9 +175,6 @@
   </si>
   <si>
     <t>4h warm quiet acquisition with DAQ board disconnected for tile R, fast hk sampling time x10</t>
-  </si>
-  <si>
-    <t>Y factor test + offset_PS6 (new bias)</t>
   </si>
   <si>
     <t>2025_06_13_13-49-09.h5</t>
@@ -347,14 +326,119 @@
     <t>60780.72778963765</t>
   </si>
   <si>
-    <t>QUELLI EVIDENZIATI SONO STATI UTILIZZATI NELL'ANALISI DATI</t>
+    <t>2026_02_07_04-54-15.h5</t>
+  </si>
+  <si>
+    <t>2026_02_07_08-54-15.h5</t>
+  </si>
+  <si>
+    <t>2026_02_07_12-54-15.h5</t>
+  </si>
+  <si>
+    <t>2026_02_07_16-54-15.h5</t>
+  </si>
+  <si>
+    <t>2026_02_07_20-54-15.h5</t>
+  </si>
+  <si>
+    <t>2026_02_20_02-41-19.h5</t>
+  </si>
+  <si>
+    <t>2026_02_20_06-41-19.h5</t>
+  </si>
+  <si>
+    <t>2026_02_20_10-41-19.h5</t>
+  </si>
+  <si>
+    <t>2026_02_20_14-41-19.h5</t>
+  </si>
+  <si>
+    <t>2026_02_20_18-41-19.h5</t>
+  </si>
+  <si>
+    <t>2026_02_20_22-41-19.h5</t>
+  </si>
+  <si>
+    <t>4h cryo quiet acquisition (old bias)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Y factor test + offset_PS6/offsetVD0 (old bias)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y factor test + offset_PS6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4h cryo quiet acquisition </t>
+  </si>
+  <si>
+    <t>COMMENTS</t>
+  </si>
+  <si>
+    <t>Board O not working</t>
+  </si>
+  <si>
+    <t>Board B not working</t>
+  </si>
+  <si>
+    <t>Board B and O turned off</t>
+  </si>
+  <si>
+    <t>2026_03_02_05-05-49.h5</t>
+  </si>
+  <si>
+    <t>2026_03_02_09-05-49.h5</t>
+  </si>
+  <si>
+    <t>2026_03_02_13-05-49.h5</t>
+  </si>
+  <si>
+    <t>2026_03_02_17-05-49.h5</t>
+  </si>
+  <si>
+    <t>2026_03_02_21-05-49.h5</t>
+  </si>
+  <si>
+    <t>2026_03_02_01-05-49.h5</t>
+  </si>
+  <si>
+    <t>Board V not working</t>
+  </si>
+  <si>
+    <t>Turn on/off board Y (X-talk test on board Y polarimeters)</t>
+  </si>
+  <si>
+    <t>Board B turned off</t>
+  </si>
+  <si>
+    <t>All boards turned off</t>
+  </si>
+  <si>
+    <t>CRYO-COOLER REPLACEMENT</t>
+  </si>
+  <si>
+    <t>4h warm quiet acquisition (closed cryostat)</t>
+  </si>
+  <si>
+    <t>POLARIMETERS BIAS UPDATE</t>
+  </si>
+  <si>
+    <t>Hightighted files were used in data analysis</t>
+  </si>
+  <si>
+    <t>INSTRUMENT COOLING DOWN</t>
+  </si>
+  <si>
+    <t>INSTRUMENT WARMING UP</t>
+  </si>
+  <si>
+    <t>HARNESS DE-INTEGRATION</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -371,13 +455,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color theme="1"/>
@@ -386,6 +463,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -406,7 +498,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -439,19 +531,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -472,30 +551,10 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -520,61 +579,50 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -855,551 +903,873 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="87.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D2" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="E2" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="F2" s="31" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="3">
         <v>45659</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="38" t="s">
-        <v>65</v>
-      </c>
-      <c r="E3" s="38" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+      <c r="C3" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="11">
         <v>45659</v>
       </c>
-      <c r="C4" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="38"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+      <c r="C4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" t="s">
+        <v>108</v>
+      </c>
+      <c r="F4" s="20"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="13">
         <v>45659</v>
       </c>
-      <c r="C5" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="26" t="s">
+      <c r="C5" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="3">
         <v>45694</v>
       </c>
       <c r="C6" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="B7" s="9"/>
+      <c r="C7" s="26"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="E6" s="38" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
+      <c r="B8" s="7">
+        <v>45722</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B9" s="3">
         <v>45722</v>
       </c>
-      <c r="C7" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="D7" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="E7" s="38" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="C9" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9" t="s">
+        <v>109</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="3">
-        <v>45722</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="38" t="s">
-        <v>66</v>
-      </c>
-      <c r="E8" s="38" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
+      <c r="B10" s="11">
+        <v>45723</v>
+      </c>
+      <c r="C10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D10" t="s">
+        <v>109</v>
+      </c>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B11" s="13">
         <v>45723</v>
       </c>
-      <c r="C9" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+      <c r="C11" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="D11" t="s">
+        <v>109</v>
+      </c>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
         <v>9</v>
-      </c>
-      <c r="B10" s="18">
-        <v>45723</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="21">
-        <v>45725</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
-        <v>11</v>
       </c>
       <c r="B12" s="15">
         <v>45725</v>
       </c>
-      <c r="C12" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="C12" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" t="s">
+        <v>109</v>
+      </c>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="11">
+        <v>45725</v>
+      </c>
+      <c r="C13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" t="s">
+        <v>109</v>
+      </c>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="13">
+        <v>45725</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="18">
-        <v>45725</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
+      <c r="B15" s="9">
+        <v>45726</v>
+      </c>
+      <c r="C15" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="12">
-        <v>45726</v>
-      </c>
-      <c r="C14" s="13" t="s">
+      <c r="D15" t="s">
+        <v>109</v>
+      </c>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
+      <c r="B16" s="15">
+        <v>45727</v>
+      </c>
+      <c r="C16" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="12">
+      <c r="D16" t="s">
+        <v>109</v>
+      </c>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="B17" s="9"/>
+      <c r="C17" s="26"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="13">
         <v>45727</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C18" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
+      <c r="D18" t="s">
+        <v>109</v>
+      </c>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="12">
-        <v>45727</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+      <c r="B19" s="5">
+        <v>45756</v>
+      </c>
+      <c r="C19" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="6">
+      <c r="D19" t="s">
+        <v>110</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="5">
         <v>45756</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C20" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="38" t="s">
+      <c r="D20" t="s">
+        <v>110</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="11">
+        <v>45758</v>
+      </c>
+      <c r="C21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" t="s">
+        <v>110</v>
+      </c>
+      <c r="F21" s="20"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="5">
+        <v>45758</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" t="s">
+        <v>110</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="5">
+        <v>45758</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23" t="s">
+        <v>110</v>
+      </c>
+      <c r="E23" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="E17" s="38" t="s">
+      <c r="F23" s="20" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="6">
-        <v>45756</v>
-      </c>
-      <c r="C18" s="7" t="s">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="5">
+        <v>45758</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="D24" t="s">
+        <v>110</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" s="11">
+        <v>45759</v>
+      </c>
+      <c r="C25" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25" t="s">
+        <v>110</v>
+      </c>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="E18" s="38" t="s">
+      <c r="B26" s="7">
+        <v>45761</v>
+      </c>
+      <c r="C26" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="D26" t="s">
+        <v>110</v>
+      </c>
+      <c r="E26" s="20" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="15">
-        <v>45758</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="E19" s="38"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="6">
-        <v>45758</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" s="38" t="s">
+      <c r="F26" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="E20" s="38" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="6">
-        <v>45758</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="E21" s="38" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="6">
-        <v>45758</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D22" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="E22" s="38" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="15">
-        <v>45759</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="9">
-        <v>45761</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="D24" s="38" t="s">
-        <v>79</v>
-      </c>
-      <c r="E24" s="38" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="29" t="s">
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="17">
+        <v>45762</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" t="s">
+        <v>110</v>
+      </c>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="19">
+        <v>45762</v>
+      </c>
+      <c r="C28" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D28" t="s">
+        <v>120</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="30">
+      <c r="B29" s="19">
         <v>45762</v>
       </c>
-      <c r="C25" s="31" t="s">
+      <c r="C29" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" t="s">
+        <v>120</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="19">
+        <v>45762</v>
+      </c>
+      <c r="C30" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" t="s">
+        <v>120</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="19">
+        <v>45762</v>
+      </c>
+      <c r="C31" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="D31" t="s">
+        <v>120</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" s="19">
+        <v>45762</v>
+      </c>
+      <c r="C32" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32" t="s">
+        <v>120</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F32" s="20" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="B33" s="17"/>
+      <c r="C33" s="22"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
         <v>41</v>
-      </c>
-      <c r="D25" s="38"/>
-      <c r="E25" s="38"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="24">
-        <v>45762</v>
-      </c>
-      <c r="C26" s="25"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" s="33">
-        <v>45762</v>
-      </c>
-      <c r="C27" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="D27" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="E27" s="38" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="36">
-        <v>45762</v>
-      </c>
-      <c r="C28" s="37" t="s">
-        <v>40</v>
-      </c>
-      <c r="D28" s="38" t="s">
-        <v>90</v>
-      </c>
-      <c r="E28" s="38" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="36">
-        <v>45762</v>
-      </c>
-      <c r="C29" s="37" t="s">
-        <v>42</v>
-      </c>
-      <c r="D29" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="E29" s="38" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="35" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="36">
-        <v>45762</v>
-      </c>
-      <c r="C30" s="37" t="s">
-        <v>43</v>
-      </c>
-      <c r="D30" s="38" t="s">
-        <v>92</v>
-      </c>
-      <c r="E30" s="38" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="35" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="36">
-        <v>45762</v>
-      </c>
-      <c r="C31" s="37" t="s">
-        <v>64</v>
-      </c>
-      <c r="D31" s="38" t="s">
-        <v>93</v>
-      </c>
-      <c r="E31" s="38" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="B32" s="21">
-        <v>45820</v>
-      </c>
-      <c r="C32" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="D32" s="38"/>
-      <c r="E32" s="38"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B33" s="15">
-        <v>45820</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="D33" s="38"/>
-      <c r="E33" s="38"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
-        <v>47</v>
       </c>
       <c r="B34" s="15">
         <v>45820</v>
       </c>
-      <c r="C34" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="D34" s="38"/>
-      <c r="E34" s="38"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="B35" s="15">
+      <c r="C34" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="D34" t="s">
+        <v>119</v>
+      </c>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="11">
         <v>45820</v>
       </c>
-      <c r="C35" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="D35" s="38"/>
-      <c r="E35" s="38"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="14" t="s">
+      <c r="C35" t="s">
+        <v>54</v>
+      </c>
+      <c r="D35" t="s">
+        <v>119</v>
+      </c>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="11">
+        <v>45820</v>
+      </c>
+      <c r="C36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D36" t="s">
+        <v>119</v>
+      </c>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="11">
+        <v>45821</v>
+      </c>
+      <c r="C37" t="s">
+        <v>55</v>
+      </c>
+      <c r="D37" t="s">
+        <v>119</v>
+      </c>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B36" s="15">
+      <c r="B38" s="7">
         <v>45821</v>
       </c>
-      <c r="C36" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="D36" s="38"/>
-      <c r="E36" s="38"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B37" s="9">
-        <v>45821</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="D37" s="38" t="s">
-        <v>81</v>
-      </c>
-      <c r="E37" s="38" t="s">
-        <v>82</v>
+      <c r="C38" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="D38" t="s">
+        <v>119</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F38" s="20" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="B40" s="15">
+        <v>46060</v>
+      </c>
+      <c r="C40" s="25" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B41" s="11">
+        <v>46060</v>
+      </c>
+      <c r="C41" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B42" s="11">
+        <v>46060</v>
+      </c>
+      <c r="C42" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="B43" s="11">
+        <v>46060</v>
+      </c>
+      <c r="C43" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B44" s="13">
+        <v>46060</v>
+      </c>
+      <c r="C44" s="24" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="B45" s="9"/>
+      <c r="C45" s="26"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B46" s="11">
+        <v>46073</v>
+      </c>
+      <c r="C46" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="B47" s="35">
+        <v>46073</v>
+      </c>
+      <c r="C47" s="36" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B48" s="11">
+        <v>46073</v>
+      </c>
+      <c r="C48" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="B49" s="11">
+        <v>46073</v>
+      </c>
+      <c r="C49" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B50" s="11">
+        <v>46073</v>
+      </c>
+      <c r="C50" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="B51" s="13">
+        <v>46073</v>
+      </c>
+      <c r="C51" s="24" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="B52" s="15">
+        <v>46083</v>
+      </c>
+      <c r="C52" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="D52" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="B53" s="11">
+        <v>46084</v>
+      </c>
+      <c r="C53" t="s">
+        <v>0</v>
+      </c>
+      <c r="D53" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B54" s="11">
+        <v>46085</v>
+      </c>
+      <c r="C54" t="s">
+        <v>0</v>
+      </c>
+      <c r="D54" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="B55" s="11">
+        <v>46086</v>
+      </c>
+      <c r="C55" t="s">
+        <v>0</v>
+      </c>
+      <c r="D55" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="B56" s="11">
+        <v>46087</v>
+      </c>
+      <c r="C56" t="s">
+        <v>0</v>
+      </c>
+      <c r="D56" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="B57" s="13">
+        <v>46088</v>
+      </c>
+      <c r="C57" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="D57" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/HDF5_files.xlsx
+++ b/HDF5_files.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guido\Desktop\Nuova cartella\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0036A524-B848-4E67-9A8B-F21A37DE7502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F07204-6EFB-4B52-8438-B0A9BD50D196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -583,7 +583,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -620,9 +620,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1633,14 +1630,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:6" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="34" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="B47" s="35">
+      <c r="B47" s="11">
         <v>46073</v>
       </c>
-      <c r="C47" s="36" t="s">
+      <c r="C47" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1706,8 +1703,8 @@
       <c r="A53" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="B53" s="11">
-        <v>46084</v>
+      <c r="B53" s="15">
+        <v>46083</v>
       </c>
       <c r="C53" t="s">
         <v>0</v>
@@ -1720,8 +1717,8 @@
       <c r="A54" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="B54" s="11">
-        <v>46085</v>
+      <c r="B54" s="15">
+        <v>46083</v>
       </c>
       <c r="C54" t="s">
         <v>0</v>
@@ -1734,8 +1731,8 @@
       <c r="A55" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="B55" s="11">
-        <v>46086</v>
+      <c r="B55" s="15">
+        <v>46083</v>
       </c>
       <c r="C55" t="s">
         <v>0</v>
@@ -1748,8 +1745,8 @@
       <c r="A56" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="B56" s="11">
-        <v>46087</v>
+      <c r="B56" s="15">
+        <v>46083</v>
       </c>
       <c r="C56" t="s">
         <v>0</v>
@@ -1762,8 +1759,8 @@
       <c r="A57" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="B57" s="13">
-        <v>46088</v>
+      <c r="B57" s="15">
+        <v>46083</v>
       </c>
       <c r="C57" s="24" t="s">
         <v>0</v>

--- a/HDF5_files.xlsx
+++ b/HDF5_files.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guido\Desktop\Nuova cartella\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F07204-6EFB-4B52-8438-B0A9BD50D196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A581C397-03C4-4690-B781-98261D318BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -583,7 +583,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -620,6 +620,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1678,7 +1679,7 @@
       <c r="A51" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="B51" s="13">
+      <c r="B51" s="34">
         <v>46073</v>
       </c>
       <c r="C51" s="24" t="s">
@@ -1703,7 +1704,7 @@
       <c r="A53" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="B53" s="15">
+      <c r="B53" s="34">
         <v>46083</v>
       </c>
       <c r="C53" t="s">
@@ -1717,7 +1718,7 @@
       <c r="A54" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="B54" s="15">
+      <c r="B54" s="34">
         <v>46083</v>
       </c>
       <c r="C54" t="s">
@@ -1731,7 +1732,7 @@
       <c r="A55" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="B55" s="15">
+      <c r="B55" s="34">
         <v>46083</v>
       </c>
       <c r="C55" t="s">
@@ -1745,7 +1746,7 @@
       <c r="A56" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="B56" s="15">
+      <c r="B56" s="34">
         <v>46083</v>
       </c>
       <c r="C56" t="s">
@@ -1759,7 +1760,7 @@
       <c r="A57" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="B57" s="15">
+      <c r="B57" s="13">
         <v>46083</v>
       </c>
       <c r="C57" s="24" t="s">
